--- a/字段名和含义取值.xlsx
+++ b/字段名和含义取值.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11460"/>
+    <workbookView windowWidth="28000" windowHeight="18120"/>
   </bookViews>
   <sheets>
     <sheet name="字段名和含义" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="107">
   <si>
     <t>字段名</t>
   </si>
@@ -61,12 +61,6 @@
   </si>
   <si>
     <t>委拍 或 收购</t>
-  </si>
-  <si>
-    <t>是否检测</t>
-  </si>
-  <si>
-    <t>是否完成车辆检测(是否检测单过审，过审则已检测反之否)</t>
   </si>
   <si>
     <t>车辆状态</t>
@@ -187,8 +181,8 @@
     <t>检测成本</t>
   </si>
   <si>
-    <t>T2检测单过审后计入：省内 85 / 省外 120 （找小欣确认）
-省内定义：85
+    <t>T2检测单过审后计入：省内 85 / 省外 120 （找丽君确认）
+省内定义：85 
 省外定义：120</t>
   </si>
   <si>
@@ -222,7 +216,7 @@
     <t>分成</t>
   </si>
   <si>
-    <t>同财务系统“分成”字段；（待技术确认指标值，待红姐确认分成字段）</t>
+    <t>同财务系统“分成”字段；（待技术确认指标值，可能是手续费）</t>
   </si>
   <si>
     <t>销售成本</t>
@@ -256,6 +250,10 @@
     </r>
   </si>
   <si>
+    <t>退车不冲正，下次同vin码不再付业务合作服务费
+咨询刘总</t>
+  </si>
+  <si>
     <t>收购车成本</t>
   </si>
   <si>
@@ -270,7 +268,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>非汽贸收购车，按车价分档(待红姐确认，仅非汽贸收购车？)</t>
+      <t>非汽贸(集团≠汽贸)收购车，按车价分档；</t>
     </r>
     <r>
       <rPr>
@@ -314,8 +312,11 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>售后退车场景，同车(同vin)后续不再计算？</t>
+      <t>售后退车场景，同经管报表</t>
     </r>
+  </si>
+  <si>
+    <t>？</t>
   </si>
   <si>
     <t>政企场地费</t>
@@ -387,13 +388,13 @@
     <t>毛利</t>
   </si>
   <si>
-    <t>同财务系统“毛利”字段；（待技术确认指标值，待红姐确认分成字段）</t>
+    <t>同财务系统“毛利”字段；红姐说不要了</t>
   </si>
   <si>
     <t>交易总毛利</t>
   </si>
   <si>
-    <t>唯普 + 唯普云 + 汇和 + 机拍毛利合计</t>
+    <t>唯普毛利 + 唯普云毛利 + 汇和毛利 + 机拍毛利合计</t>
   </si>
   <si>
     <t>现场交付成本</t>
@@ -407,7 +408,8 @@
   </si>
   <si>
     <t>执行现场交付的服务中心(跟进服务中心)
-举例：唯普服务中心 （待小欣确认）</t>
+举例：唯普服务中心 （问伍金辉？）
+以库位为基准，</t>
   </si>
   <si>
     <t>空中交付成本</t>
@@ -432,8 +434,12 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>过户单中，除xxx服务中心外的都归属中控（待小欣确认）</t>
+      <t>过户单中，除xxx服务中心外的都归属中控（待小欣确认）
+车辆在门店库，归属中控；排掉限定门店（小欣提供门店名单，门店列表后，交付的时候，更新逻辑）</t>
     </r>
+  </si>
+  <si>
+    <t>业务合作服务费 放到分成 前面</t>
   </si>
   <si>
     <t>空中交付跟进人</t>
@@ -458,7 +464,7 @@
     <t>绩效毛利</t>
   </si>
   <si>
-    <t>总毛利−所有成本费用项(提车费+检测成本+ 数据成本+ 销售成本 +  政企场地费 +收购车成本+业务合作费+中间商费用+现场交付成本/空中交付成本+现场过户成本 )</t>
+    <t>交易总毛利−所有成本费用项(提车费+检测成本+ 数据成本+ 销售成本 + 政企场地费 +收购车成本+业务合作服务费+垫款利息+现场交付成本/空中交付成本+现场过户成本 )</t>
   </si>
   <si>
     <t>绩效工资</t>
@@ -468,6 +474,12 @@
   </si>
   <si>
     <t>待与陈霞确认字段含义</t>
+  </si>
+  <si>
+    <t>交付成本</t>
+  </si>
+  <si>
+    <t>对应经管报表如何调整、财务报表</t>
   </si>
 </sst>
 </file>
@@ -480,7 +492,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -491,6 +503,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FFC00000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -988,137 +1007,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1128,25 +1147,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1424,6 +1452,53 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>775970</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>109220</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>859790</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="图片 3"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5850890" y="20223480"/>
+          <a:ext cx="8267700" cy="1504950"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
@@ -1686,7 +1761,7 @@
   <sheetFormatPr defaultColWidth="10.3846153846154" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="17.6153846153846" customWidth="1"/>
-    <col min="2" max="2" width="87.9807692307692" customWidth="1"/>
+    <col min="2" max="2" width="59.2307692307692" customWidth="1"/>
     <col min="3" max="3" width="41.8269230769231" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1730,20 +1805,19 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:2">
+      <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="4"/>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1867,11 +1941,11 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" ht="34" spans="1:2">
       <c r="A23" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="4" t="s">
         <v>45</v>
       </c>
     </row>
@@ -1879,23 +1953,23 @@
       <c r="A24" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="25" ht="17" spans="1:2">
-      <c r="A25" s="2" t="s">
+    <row r="25" ht="51" spans="1:2">
+      <c r="A25" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="6" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="26" ht="51" spans="1:2">
-      <c r="A26" s="3" t="s">
+    <row r="26" spans="1:2">
+      <c r="A26" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="2" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1928,199 +2002,209 @@
         <v>58</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="31" ht="26" customHeight="1" spans="1:2">
+      <c r="A31" s="3" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" s="2" t="s">
+      <c r="B31" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" s="3" t="s">
+    </row>
+    <row r="32" ht="118" spans="1:2">
+      <c r="A32" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="6" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="33" ht="101" spans="1:2">
-      <c r="A33" s="7" t="s">
+    <row r="33" ht="68" spans="1:3">
+      <c r="A33" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="8" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="34" ht="68" spans="1:2">
-      <c r="A34" s="2" t="s">
+      <c r="C33" s="9" t="s">
         <v>65</v>
       </c>
+    </row>
+    <row r="34" ht="101" spans="1:2">
+      <c r="A34" s="10" t="s">
+        <v>66</v>
+      </c>
       <c r="B34" s="8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="35" ht="101" spans="1:2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="35" ht="34" spans="1:3">
       <c r="A35" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="36" ht="34" spans="1:2">
+        <v>69</v>
+      </c>
+      <c r="C35" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
       <c r="A36" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="39" ht="320" spans="1:2">
       <c r="A39" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="40" ht="320" spans="1:2">
+        <v>77</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
       <c r="A40" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B40" s="2" t="s">
         <v>80</v>
       </c>
     </row>
+    <row r="41" ht="17" spans="1:2">
+      <c r="A41" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
+      <c r="A42" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="43" ht="84" spans="1:2">
       <c r="A43" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="44" ht="68" spans="1:2">
+        <v>85</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="44" ht="51" spans="1:2">
       <c r="A44" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="45" ht="34" spans="1:2">
       <c r="A45" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="46" ht="34" spans="1:2">
+        <v>89</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="46" ht="66" customHeight="1" spans="1:3">
       <c r="A46" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="47" ht="34" spans="1:2">
+        <v>91</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C46" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
       <c r="A47" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B47" s="8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
+        <v>94</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="48" ht="34" spans="1:2">
       <c r="A48" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="49" ht="34" spans="1:2">
+        <v>96</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
       <c r="A49" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
+        <v>98</v>
+      </c>
+      <c r="B49" s="11" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="50" ht="78" customHeight="1" spans="1:2">
       <c r="A50" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="51" ht="34" spans="1:2">
+        <v>100</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
       <c r="A51" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53" s="2"/>
-      <c r="B53" s="2"/>
+      <c r="A52" s="2"/>
+      <c r="B52" s="2"/>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="B54" s="12" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="B55" s="9" t="s">
-        <v>103</v>
+      <c r="A55" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="B55" s="12" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/字段名和含义取值.xlsx
+++ b/字段名和含义取值.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28000" windowHeight="18120"/>
+    <workbookView windowHeight="18460"/>
   </bookViews>
   <sheets>
     <sheet name="字段名和含义" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="102">
   <si>
     <t>字段名</t>
   </si>
@@ -385,12 +385,6 @@
     <t>归属机拍的毛利，同经管报表“机拍毛利”字段</t>
   </si>
   <si>
-    <t>毛利</t>
-  </si>
-  <si>
-    <t>同财务系统“毛利”字段；红姐说不要了</t>
-  </si>
-  <si>
     <t>交易总毛利</t>
   </si>
   <si>
@@ -407,9 +401,8 @@
     <t>现场交付部门</t>
   </si>
   <si>
-    <t>执行现场交付的服务中心(跟进服务中心)
-举例：唯普服务中心 （问伍金辉？）
-以库位为基准，</t>
+    <t>执行现场交付的服务中心
+举例：交付型出库的时候，车辆在唯普库，展示唯普库对应的服务中心（唯普服务中心，!!以库位为基准,区别于“现场过户部门”)</t>
   </si>
   <si>
     <t>空中交付成本</t>
@@ -423,7 +416,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">服务中心或中控
+      <t xml:space="preserve">过户服务中心或中控
 </t>
     </r>
     <r>
@@ -434,12 +427,28 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>过户单中，除xxx服务中心外的都归属中控（待小欣确认）
-车辆在门店库，归属中控；排掉限定门店（小欣提供门店名单，门店列表后，交付的时候，更新逻辑）</t>
+      <t>过户任务单中对应的服务中心；</t>
     </r>
-  </si>
-  <si>
-    <t>业务合作服务费 放到分成 前面</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>过户资料回收完毕时，车辆若在门店库，归属中控；排掉限定门店</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（小欣提供门店名单，门店列表若发生更新，历史数据不做改动）</t>
+    </r>
   </si>
   <si>
     <t>空中交付跟进人</t>
@@ -458,7 +467,8 @@
     <t>现场过户部门</t>
   </si>
   <si>
-    <t>执行过户的服务中心（唯普云服务站？待小欣确认）</t>
+    <t>执行过户的服务中心
+过户任务单中对应的服务中心；</t>
   </si>
   <si>
     <t>绩效毛利</t>
@@ -468,12 +478,6 @@
   </si>
   <si>
     <t>绩效工资</t>
-  </si>
-  <si>
-    <t>毛利调整</t>
-  </si>
-  <si>
-    <t>待与陈霞确认字段含义</t>
   </si>
   <si>
     <t>交付成本</t>
@@ -1171,8 +1175,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
@@ -1452,53 +1456,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>775970</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>109220</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>859790</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="图片 3"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5850890" y="20223480"/>
-          <a:ext cx="8267700" cy="1504950"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
@@ -1757,7 +1714,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr defaultColWidth="10.3846153846154" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="17.6153846153846" customWidth="1"/>
@@ -2091,120 +2048,105 @@
         <v>80</v>
       </c>
     </row>
-    <row r="41" ht="17" spans="1:2">
-      <c r="A41" s="10" t="s">
+    <row r="41" spans="1:2">
+      <c r="A41" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" ht="84" spans="1:2">
       <c r="A42" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="43" ht="84" spans="1:2">
+    <row r="43" ht="68" spans="1:2">
       <c r="A43" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B43" s="6" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="44" ht="51" spans="1:2">
+    <row r="44" ht="34" spans="1:2">
       <c r="A44" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="4" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="45" ht="34" spans="1:2">
+    <row r="45" ht="66" customHeight="1" spans="1:3">
       <c r="A45" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B45" s="8" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="46" ht="66" customHeight="1" spans="1:3">
+      <c r="C45" s="11"/>
+    </row>
+    <row r="46" spans="1:2">
       <c r="A46" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="B46" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C46" t="s">
+    </row>
+    <row r="47" ht="34" spans="1:2">
+      <c r="A47" s="2" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47" s="2" t="s">
+      <c r="B47" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="48" ht="34" spans="1:2">
       <c r="A48" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B48" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="B48" s="4" t="s">
+    </row>
+    <row r="49" ht="78" customHeight="1" spans="1:2">
+      <c r="A49" s="2" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49" s="2" t="s">
+      <c r="B49" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="B49" s="11" t="s">
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="2" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="50" ht="78" customHeight="1" spans="1:2">
-      <c r="A50" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>101</v>
+      <c r="B50" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52" s="2"/>
-      <c r="B52" s="2"/>
+      <c r="A51" s="2"/>
+      <c r="B51" s="2"/>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="12"/>
+      <c r="B53" s="12"/>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="12" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B54" s="12" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
-      <c r="A55" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="B55" s="12" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>